--- a/Запрещённые_предметы_итог.xlsx
+++ b/Запрещённые_предметы_итог.xlsx
@@ -139,7 +139,9 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -240,7 +242,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Посетители, попытки проноса и изъятия на 10 000 посетителей</a:t>
+              <a:t>Посетители и конверсия по месяцам</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -698,8 +700,8 @@
         <scaling>
           <logBase val="10"/>
           <orientation val="minMax"/>
-          <max val="100"/>
-          <min val="0.1"/>
+          <max val="0.01"/>
+          <min val="1e-05"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -713,13 +715,13 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Изъятий на 10 000 посетителей (логарифмическая шкала)</a:t>
+                  <a:t>Конверсия (логарифмическая шкала)</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
-        <numFmt formatCode="[&lt;1]0.0;0" sourceLinked="0"/>
+        <numFmt formatCode="[&lt;0.00005]0.000%;[&lt;0.0005]0.00%;0.0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1058,7 +1060,7 @@
   <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -1066,7 +1068,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
@@ -1429,7 +1431,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Всего попыток проноса</t>
@@ -1479,7 +1481,7 @@
     <row r="11">
       <c r="A11" s="30" t="inlineStr">
         <is>
-          <t>Данные для графика: посетители и изъятий на 10 000 посетителей (ссылки на таблицу выше)</t>
+          <t>Данные для графика: посетители и конверсия (ссылки на таблицу выше)</t>
         </is>
       </c>
     </row>
@@ -1496,32 +1498,32 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Оружие</t>
+          <t>Конв. оружие</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Колющее</t>
+          <t>Конв. колющее</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>Аэрозоль</t>
+          <t>Конв. аэрозоль</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>Спирт</t>
+          <t>Конв. спирт</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>Пиротехника</t>
+          <t>Конв. пиротехника</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>Всего</t>
+          <t>Конв. всего</t>
         </is>
       </c>
       <c r="I12" s="1" t="inlineStr">
@@ -1540,28 +1542,28 @@
         <f>B3</f>
         <v/>
       </c>
-      <c r="C13" s="13">
-        <f>D4</f>
-        <v/>
-      </c>
-      <c r="D13" s="19">
-        <f>D5</f>
-        <v/>
-      </c>
-      <c r="E13" s="19">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="F13" s="19">
-        <f>D7</f>
-        <v/>
-      </c>
-      <c r="G13" s="13">
-        <f>D8</f>
-        <v/>
-      </c>
-      <c r="H13" s="19">
-        <f>D9</f>
+      <c r="C13" s="12">
+        <f>C4</f>
+        <v/>
+      </c>
+      <c r="D13" s="18">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="E13" s="18">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="F13" s="18">
+        <f>C7</f>
+        <v/>
+      </c>
+      <c r="G13" s="12">
+        <f>C8</f>
+        <v/>
+      </c>
+      <c r="H13" s="18">
+        <f>C9</f>
         <v/>
       </c>
       <c r="I13" s="10">
@@ -1579,28 +1581,28 @@
         <f>E3</f>
         <v/>
       </c>
-      <c r="C14" s="13">
-        <f>G4</f>
-        <v/>
-      </c>
-      <c r="D14" s="19">
-        <f>G5</f>
-        <v/>
-      </c>
-      <c r="E14" s="19">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="F14" s="19">
-        <f>G7</f>
-        <v/>
-      </c>
-      <c r="G14" s="13">
-        <f>G8</f>
-        <v/>
-      </c>
-      <c r="H14" s="19">
-        <f>G9</f>
+      <c r="C14" s="12">
+        <f>F4</f>
+        <v/>
+      </c>
+      <c r="D14" s="18">
+        <f>F5</f>
+        <v/>
+      </c>
+      <c r="E14" s="18">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="F14" s="18">
+        <f>F7</f>
+        <v/>
+      </c>
+      <c r="G14" s="12">
+        <f>F8</f>
+        <v/>
+      </c>
+      <c r="H14" s="18">
+        <f>F9</f>
         <v/>
       </c>
       <c r="I14" s="10">
@@ -1608,7 +1610,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="B15" s="32">
         <f>"Посетители ("&amp;IF(I3&gt;0,"+","")&amp;ROUND(I3*100,1)&amp;"%"&amp;")"</f>
         <v/>

--- a/Запрещённые_предметы_итог.xlsx
+++ b/Запрещённые_предметы_итог.xlsx
@@ -281,7 +281,7 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Досмотр'!$I$13:$I$14</f>
+              <f>'Досмотр'!$A$13:$A$14</f>
             </numRef>
           </cat>
           <val>
@@ -337,7 +337,7 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Досмотр'!$I$13:$I$14</f>
+              <f>'Досмотр'!$A$13:$A$14</f>
             </numRef>
           </cat>
           <val>
@@ -397,7 +397,7 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Досмотр'!$I$13:$I$14</f>
+              <f>'Досмотр'!$A$13:$A$14</f>
             </numRef>
           </cat>
           <val>
@@ -448,7 +448,7 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Досмотр'!$I$13:$I$14</f>
+              <f>'Досмотр'!$A$13:$A$14</f>
             </numRef>
           </cat>
           <val>
@@ -499,7 +499,7 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Досмотр'!$I$13:$I$14</f>
+              <f>'Досмотр'!$A$13:$A$14</f>
             </numRef>
           </cat>
           <val>
@@ -550,7 +550,7 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Досмотр'!$I$13:$I$14</f>
+              <f>'Досмотр'!$A$13:$A$14</f>
             </numRef>
           </cat>
           <val>
@@ -601,52 +601,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Досмотр'!$I$13:$I$14</f>
+              <f>'Досмотр'!$A$13:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Досмотр'!$G$13:$G$14</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <v> </v>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="b"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="1"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'Досмотр'!$I$13:$I$14</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Досмотр'!$H$13:$H$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -659,7 +619,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="1"/>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -730,10 +690,6 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
-      <legendEntry>
-        <idx val="7"/>
-        <delete val="1"/>
-      </legendEntry>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1068,7 +1024,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
@@ -1526,11 +1482,6 @@
           <t>Конв. всего</t>
         </is>
       </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>Подпись под точкой</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1566,10 +1517,6 @@
         <f>C9</f>
         <v/>
       </c>
-      <c r="I13" s="10">
-        <f>A13&amp;", попыток: "&amp;IF(B9&gt;=1000,INT(B9/1000)&amp;" "&amp;TEXT(MOD(B9,1000),"000"),B9)</f>
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -1603,10 +1550,6 @@
       </c>
       <c r="H14" s="18">
         <f>F9</f>
-        <v/>
-      </c>
-      <c r="I14" s="10">
-        <f>A14&amp;", попыток: "&amp;IF(E9&gt;=1000,INT(E9/1000)&amp;" "&amp;TEXT(MOD(E9,1000),"000"),E9)</f>
         <v/>
       </c>
     </row>

--- a/Запрещённые_предметы_итог.xlsx
+++ b/Запрещённые_предметы_итог.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t xml:space="preserve">Показатель</t>
   </si>
@@ -40,16 +40,10 @@
     <t xml:space="preserve">Конверсия</t>
   </si>
   <si>
-    <t xml:space="preserve">На 10 000 посетителей</t>
-  </si>
-  <si>
     <t xml:space="preserve">Кол-во, шт</t>
   </si>
   <si>
     <t xml:space="preserve">Кол-во, %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">На 10 000</t>
   </si>
   <si>
     <t xml:space="preserve">Конверсия, п.п.</t>
@@ -110,20 +104,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="\+#,##0;\-#,##0;0"/>
-    <numFmt numFmtId="169" formatCode="\+0.0%;\-0.0%;0.0%"/>
-    <numFmt numFmtId="170" formatCode="\+0.0;\-0.0;0.0"/>
-    <numFmt numFmtId="171" formatCode="\+0.000;\-0.000;0.000"/>
-    <numFmt numFmtId="172" formatCode="0.0000%"/>
-    <numFmt numFmtId="173" formatCode="0.00"/>
-    <numFmt numFmtId="174" formatCode="\+0.00;\-0.00;0.00"/>
-    <numFmt numFmtId="175" formatCode="\+0.0000;\-0.0000;0.0000"/>
-    <numFmt numFmtId="176" formatCode="[&lt;0.00005]0.000%;[&lt;0.0005]0.00%;0.0%"/>
+    <numFmt numFmtId="167" formatCode="\+#,##0;\-#,##0;0"/>
+    <numFmt numFmtId="168" formatCode="\+0.0%;\-0.0%;0.0%"/>
+    <numFmt numFmtId="169" formatCode="\+0.000;\-0.000;0.000"/>
+    <numFmt numFmtId="170" formatCode="0.0000%"/>
+    <numFmt numFmtId="171" formatCode="\+0.0000;\-0.0000;0.0000"/>
+    <numFmt numFmtId="172" formatCode="[&lt;0.00005]0.000%;[&lt;0.0005]0.00%;0.0%"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -272,7 +262,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -293,23 +283,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -321,11 +303,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -333,34 +315,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -382,14 +348,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -614,8 +572,8 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="88724169"/>
-        <c:axId val="72301386"/>
+        <c:axId val="60963552"/>
+        <c:axId val="74677924"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1291,11 +1249,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="71118634"/>
-        <c:axId val="76694814"/>
+        <c:axId val="56200164"/>
+        <c:axId val="98417295"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="88724169"/>
+        <c:axId val="60963552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1328,7 +1286,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72301386"/>
+        <c:crossAx val="74677924"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1336,7 +1294,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72301386"/>
+        <c:axId val="74677924"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1000000"/>
@@ -1404,12 +1362,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88724169"/>
+        <c:crossAx val="60963552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="71118634"/>
+        <c:axId val="56200164"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1442,7 +1400,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76694814"/>
+        <c:crossAx val="98417295"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1450,7 +1408,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76694814"/>
+        <c:axId val="98417295"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -1519,7 +1477,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71118634"/>
+        <c:crossAx val="56200164"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1800,8 +1758,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>838440</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>227160</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>2880</xdr:rowOff>
     </xdr:to>
@@ -2005,11 +1963,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2020,18 +1978,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
@@ -2042,430 +1997,340 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>436644</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>484265</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <f aca="false">E3-B3</f>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <f aca="false">D3-B3</f>
         <v>47621</v>
       </c>
-      <c r="I3" s="7" t="n">
-        <f aca="false">IF(B3=0,"-",E3/B3-1)</f>
+      <c r="G3" s="6" t="n">
+        <f aca="false">IF(B3=0,"-",D3/B3-1)</f>
         <v>0.109061386392576</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>12</v>
+      <c r="H3" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="11" t="n">
+      <c r="A4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="10" t="n">
         <f aca="false">B4/$B$3</f>
         <v>5.49646851897656E-005</v>
       </c>
-      <c r="D4" s="13" t="n">
-        <f aca="false">C4*10000</f>
-        <v>0.549646851897656</v>
-      </c>
-      <c r="E4" s="11" t="n">
+      <c r="D4" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="12" t="n">
-        <f aca="false">E4/$E$3</f>
+      <c r="E4" s="10" t="n">
+        <f aca="false">D4/$D$3</f>
         <v>6.19495524144838E-005</v>
       </c>
-      <c r="G4" s="13" t="n">
-        <f aca="false">F4*10000</f>
-        <v>0.619495524144838</v>
-      </c>
-      <c r="H4" s="14" t="n">
-        <f aca="false">E4-B4</f>
+      <c r="F4" s="11" t="n">
+        <f aca="false">D4-B4</f>
         <v>6</v>
       </c>
-      <c r="I4" s="15" t="n">
-        <f aca="false">IF(B4=0,"-",E4/B4-1)</f>
+      <c r="G4" s="12" t="n">
+        <f aca="false">IF(B4=0,"-",D4/B4-1)</f>
         <v>0.25</v>
       </c>
-      <c r="J4" s="16" t="n">
-        <f aca="false">G4-D4</f>
-        <v>0.0698486722471824</v>
-      </c>
-      <c r="K4" s="17" t="n">
-        <f aca="false">(F4-C4)*100</f>
+      <c r="H4" s="13" t="n">
+        <f aca="false">(E4-C4)*100</f>
         <v>0.000698486722471824</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="11" t="n">
+      <c r="A5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>1716</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="14" t="n">
         <f aca="false">B5/$B$3</f>
         <v>0.00392997499106824</v>
       </c>
-      <c r="D5" s="19" t="n">
-        <f aca="false">C5*10000</f>
-        <v>39.2997499106824</v>
-      </c>
-      <c r="E5" s="11" t="n">
+      <c r="D5" s="9" t="n">
         <v>1698</v>
       </c>
-      <c r="F5" s="18" t="n">
-        <f aca="false">E5/$E$3</f>
+      <c r="E5" s="14" t="n">
+        <f aca="false">D5/$D$3</f>
         <v>0.00350634466665978</v>
       </c>
-      <c r="G5" s="19" t="n">
-        <f aca="false">F5*10000</f>
-        <v>35.0634466665978</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <f aca="false">E5-B5</f>
+      <c r="F5" s="11" t="n">
+        <f aca="false">D5-B5</f>
         <v>-18</v>
       </c>
-      <c r="I5" s="15" t="n">
-        <f aca="false">IF(B5=0,"-",E5/B5-1)</f>
+      <c r="G5" s="12" t="n">
+        <f aca="false">IF(B5=0,"-",D5/B5-1)</f>
         <v>-0.0104895104895105</v>
       </c>
-      <c r="J5" s="20" t="n">
-        <f aca="false">G5-D5</f>
-        <v>-4.23630324408455</v>
-      </c>
-      <c r="K5" s="21" t="n">
-        <f aca="false">(F5-C5)*100</f>
+      <c r="H5" s="15" t="n">
+        <f aca="false">(E5-C5)*100</f>
         <v>-0.0423630324408455</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="11" t="n">
+      <c r="A6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>871</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="14" t="n">
         <f aca="false">B6/$B$3</f>
         <v>0.00199476003334524</v>
       </c>
-      <c r="D6" s="19" t="n">
-        <f aca="false">C6*10000</f>
-        <v>19.9476003334524</v>
-      </c>
-      <c r="E6" s="11" t="n">
+      <c r="D6" s="9" t="n">
         <v>661</v>
       </c>
-      <c r="F6" s="18" t="n">
-        <f aca="false">E6/$E$3</f>
+      <c r="E6" s="14" t="n">
+        <f aca="false">D6/$D$3</f>
         <v>0.00136495513819913</v>
       </c>
-      <c r="G6" s="19" t="n">
-        <f aca="false">F6*10000</f>
-        <v>13.6495513819913</v>
-      </c>
-      <c r="H6" s="14" t="n">
-        <f aca="false">E6-B6</f>
+      <c r="F6" s="11" t="n">
+        <f aca="false">D6-B6</f>
         <v>-210</v>
       </c>
-      <c r="I6" s="15" t="n">
-        <f aca="false">IF(B6=0,"-",E6/B6-1)</f>
+      <c r="G6" s="12" t="n">
+        <f aca="false">IF(B6=0,"-",D6/B6-1)</f>
         <v>-0.241102181400689</v>
       </c>
-      <c r="J6" s="20" t="n">
-        <f aca="false">G6-D6</f>
-        <v>-6.29804895146116</v>
-      </c>
-      <c r="K6" s="21" t="n">
-        <f aca="false">(F6-C6)*100</f>
+      <c r="H6" s="15" t="n">
+        <f aca="false">(E6-C6)*100</f>
         <v>-0.0629804895146116</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="11" t="n">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="9" t="n">
         <v>569</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="14" t="n">
         <f aca="false">B7/$B$3</f>
         <v>0.00130312107804069</v>
       </c>
-      <c r="D7" s="19" t="n">
-        <f aca="false">C7*10000</f>
-        <v>13.0312107804069</v>
-      </c>
-      <c r="E7" s="11" t="n">
+      <c r="D7" s="9" t="n">
         <v>578</v>
       </c>
-      <c r="F7" s="18" t="n">
-        <f aca="false">E7/$E$3</f>
+      <c r="E7" s="14" t="n">
+        <f aca="false">D7/$D$3</f>
         <v>0.00119356137651905</v>
       </c>
-      <c r="G7" s="19" t="n">
-        <f aca="false">F7*10000</f>
-        <v>11.9356137651905</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <f aca="false">E7-B7</f>
+      <c r="F7" s="11" t="n">
+        <f aca="false">D7-B7</f>
         <v>9</v>
       </c>
-      <c r="I7" s="15" t="n">
-        <f aca="false">IF(B7=0,"-",E7/B7-1)</f>
+      <c r="G7" s="12" t="n">
+        <f aca="false">IF(B7=0,"-",D7/B7-1)</f>
         <v>0.015817223198594</v>
       </c>
-      <c r="J7" s="20" t="n">
-        <f aca="false">G7-D7</f>
-        <v>-1.09559701521637</v>
-      </c>
-      <c r="K7" s="21" t="n">
-        <f aca="false">(F7-C7)*100</f>
+      <c r="H7" s="15" t="n">
+        <f aca="false">(E7-C7)*100</f>
         <v>-0.0109559701521637</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="11" t="n">
+      <c r="A8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="10" t="n">
         <f aca="false">B8/$B$3</f>
         <v>1.14509760812012E-005</v>
       </c>
-      <c r="D8" s="13" t="n">
-        <f aca="false">C8*10000</f>
-        <v>0.114509760812012</v>
-      </c>
-      <c r="E8" s="11" t="n">
+      <c r="D8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="12" t="n">
-        <f aca="false">E8/$E$3</f>
+      <c r="E8" s="10" t="n">
+        <f aca="false">D8/$D$3</f>
         <v>1.44548955633796E-005</v>
       </c>
-      <c r="G8" s="13" t="n">
-        <f aca="false">F8*10000</f>
-        <v>0.144548955633796</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <f aca="false">E8-B8</f>
+      <c r="F8" s="11" t="n">
+        <f aca="false">D8-B8</f>
         <v>2</v>
       </c>
-      <c r="I8" s="15" t="n">
-        <f aca="false">IF(B8=0,"-",E8/B8-1)</f>
+      <c r="G8" s="12" t="n">
+        <f aca="false">IF(B8=0,"-",D8/B8-1)</f>
         <v>0.4</v>
       </c>
-      <c r="J8" s="16" t="n">
-        <f aca="false">G8-D8</f>
-        <v>0.0300391948217839</v>
-      </c>
-      <c r="K8" s="17" t="n">
-        <f aca="false">(F8-C8)*100</f>
+      <c r="H8" s="13" t="n">
+        <f aca="false">(E8-C8)*100</f>
         <v>0.000300391948217839</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="23" t="n">
+      <c r="A9" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="17" t="n">
         <f aca="false">SUM(B4:B8)</f>
         <v>3185</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="18" t="n">
         <f aca="false">B9/$B$3</f>
         <v>0.00729427176372514</v>
       </c>
-      <c r="D9" s="25" t="n">
-        <f aca="false">C9*10000</f>
-        <v>72.9427176372514</v>
-      </c>
-      <c r="E9" s="23" t="n">
-        <f aca="false">SUM(E4:E8)</f>
+      <c r="D9" s="17" t="n">
+        <f aca="false">SUM(D4:D8)</f>
         <v>2974</v>
       </c>
-      <c r="F9" s="24" t="n">
-        <f aca="false">E9/$E$3</f>
+      <c r="E9" s="18" t="n">
+        <f aca="false">D9/$D$3</f>
         <v>0.00614126562935583</v>
       </c>
-      <c r="G9" s="25" t="n">
-        <f aca="false">F9*10000</f>
-        <v>61.4126562935583</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <f aca="false">E9-B9</f>
+      <c r="F9" s="19" t="n">
+        <f aca="false">D9-B9</f>
         <v>-211</v>
       </c>
-      <c r="I9" s="27" t="n">
-        <f aca="false">IF(B9=0,"-",E9/B9-1)</f>
+      <c r="G9" s="20" t="n">
+        <f aca="false">IF(B9=0,"-",D9/B9-1)</f>
         <v>-0.0662480376766091</v>
       </c>
-      <c r="J9" s="28" t="n">
-        <f aca="false">G9-D9</f>
-        <v>-11.5300613436931</v>
-      </c>
-      <c r="K9" s="29" t="n">
-        <f aca="false">(F9-C9)*100</f>
+      <c r="H9" s="21" t="n">
+        <f aca="false">(E9-C9)*100</f>
         <v>-0.115300613436931</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="s">
-        <v>19</v>
+      <c r="A11" s="22" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="23" t="n">
         <f aca="false">B3</f>
         <v>436644</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="10" t="n">
         <f aca="false">C4</f>
         <v>5.49646851897656E-005</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="14" t="n">
         <f aca="false">C5</f>
         <v>0.00392997499106824</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="14" t="n">
         <f aca="false">C6</f>
         <v>0.00199476003334524</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="14" t="n">
         <f aca="false">C7</f>
         <v>0.00130312107804069</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="10" t="n">
         <f aca="false">C8</f>
         <v>1.14509760812012E-005</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="14" t="n">
         <f aca="false">C9</f>
         <v>0.00729427176372514</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="31" t="n">
-        <f aca="false">E3</f>
+      <c r="B14" s="23" t="n">
+        <f aca="false">D3</f>
         <v>484265</v>
       </c>
-      <c r="C14" s="12" t="n">
-        <f aca="false">F4</f>
+      <c r="C14" s="10" t="n">
+        <f aca="false">E4</f>
         <v>6.19495524144838E-005</v>
       </c>
-      <c r="D14" s="18" t="n">
-        <f aca="false">F5</f>
+      <c r="D14" s="14" t="n">
+        <f aca="false">E5</f>
         <v>0.00350634466665978</v>
       </c>
-      <c r="E14" s="18" t="n">
-        <f aca="false">F6</f>
+      <c r="E14" s="14" t="n">
+        <f aca="false">E6</f>
         <v>0.00136495513819913</v>
       </c>
-      <c r="F14" s="18" t="n">
-        <f aca="false">F7</f>
+      <c r="F14" s="14" t="n">
+        <f aca="false">E7</f>
         <v>0.00119356137651905</v>
       </c>
-      <c r="G14" s="12" t="n">
-        <f aca="false">F8</f>
+      <c r="G14" s="10" t="n">
+        <f aca="false">E8</f>
         <v>1.44548955633796E-005</v>
       </c>
-      <c r="H14" s="18" t="n">
-        <f aca="false">F9</f>
+      <c r="H14" s="14" t="n">
+        <f aca="false">E9</f>
         <v>0.00614126562935583</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:K1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:H1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
